--- a/pregenerated_results/att_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
+++ b/pregenerated_results/att_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,10 +510,10 @@
         <v>-0.037</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="E3" t="n">
-        <v>0.034</v>
+        <v>0.033</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.024</v>
+        <v>-0.066</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.002</v>
+        <v>0.007</v>
       </c>
       <c r="E7" t="n">
-        <v>0.022</v>
+        <v>0.059</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.046</v>
+        <v>0.227</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="E8" t="n">
-        <v>0.045</v>
+        <v>0.225</v>
       </c>
       <c r="F8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.392</v>
       </c>
       <c r="D9" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="F9" t="b">
         <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="F9" t="b">
-        <v>1</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,16 +696,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.074</v>
+        <v>-0.401</v>
       </c>
       <c r="D10" t="n">
         <v>0.004</v>
       </c>
       <c r="E10" t="n">
-        <v>0.06999999999999999</v>
+        <v>0.397</v>
       </c>
       <c r="F10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.034</v>
+        <v>-0.054</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
       <c r="E11" t="n">
-        <v>0.033</v>
+        <v>0.048</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.023</v>
+        <v>0.077</v>
       </c>
       <c r="D12" t="n">
-        <v>0.004</v>
+        <v>-0.001</v>
       </c>
       <c r="E12" t="n">
-        <v>0.019</v>
+        <v>0.076</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.007</v>
+        <v>-0.008</v>
       </c>
       <c r="D13" t="n">
-        <v>0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="E13" t="n">
         <v>0.006</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,13 +804,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.041</v>
+        <v>0.007</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.001</v>
       </c>
       <c r="E14" t="n">
-        <v>0.032</v>
+        <v>0.006</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.005</v>
+        <v>0.032</v>
       </c>
       <c r="D15" t="n">
-        <v>0.007</v>
+        <v>-0.004</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.002</v>
+        <v>0.028</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.032</v>
+        <v>0.022</v>
       </c>
       <c r="D16" t="n">
         <v>-0.004</v>
       </c>
       <c r="E16" t="n">
-        <v>0.028</v>
+        <v>0.018</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.014</v>
+        <v>0.005</v>
       </c>
       <c r="D17" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="E17" t="n">
-        <v>0.012</v>
+        <v>-0.002</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,16 +912,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0</v>
+        <v>0.197</v>
       </c>
       <c r="D18" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="F18" t="b">
         <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="b">
-        <v>1</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.008</v>
+        <v>-0.143</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.002</v>
+        <v>0.003</v>
       </c>
       <c r="E19" t="n">
-        <v>0.006</v>
+        <v>0.14</v>
       </c>
       <c r="F19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.077</v>
+        <v>0.034</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.001</v>
+        <v>0.001</v>
       </c>
       <c r="E20" t="n">
-        <v>0.076</v>
+        <v>0.033</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.019</v>
+        <v>-0</v>
       </c>
       <c r="D21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.113</v>
+        <v>-0.019</v>
       </c>
       <c r="D22" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0.11</v>
+        <v>0.019</v>
       </c>
       <c r="F22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.197</v>
+        <v>-0.128</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.006</v>
+        <v>-0.002</v>
       </c>
       <c r="E23" t="n">
-        <v>0.191</v>
+        <v>0.126</v>
       </c>
       <c r="F23" t="b">
         <v>0</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,16 +1074,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.143</v>
+        <v>-0.074</v>
       </c>
       <c r="D24" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="E24" t="n">
-        <v>0.14</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="F24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,16 +1101,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.054</v>
+        <v>0.107</v>
       </c>
       <c r="D25" t="n">
-        <v>0.006</v>
+        <v>-0.003</v>
       </c>
       <c r="E25" t="n">
-        <v>0.048</v>
+        <v>0.104</v>
       </c>
       <c r="F25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,16 +1128,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-0.128</v>
+        <v>-0.014</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.002</v>
+        <v>0.002</v>
       </c>
       <c r="E26" t="n">
-        <v>0.126</v>
+        <v>0.012</v>
       </c>
       <c r="F26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,16 +1155,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.227</v>
+        <v>0.046</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="E27" t="n">
-        <v>0.225</v>
+        <v>0.045</v>
       </c>
       <c r="F27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,16 +1182,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.392</v>
+        <v>-0.041</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.008</v>
+        <v>-0.001</v>
       </c>
       <c r="E28" t="n">
-        <v>0.384</v>
+        <v>0.04</v>
       </c>
       <c r="F28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,16 +1209,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.401</v>
+        <v>0.041</v>
       </c>
       <c r="D29" t="n">
-        <v>0.005</v>
+        <v>-0.008</v>
       </c>
       <c r="E29" t="n">
-        <v>0.396</v>
+        <v>0.033</v>
       </c>
       <c r="F29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,16 +1236,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.107</v>
+        <v>-0.024</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.003</v>
+        <v>-0.002</v>
       </c>
       <c r="E30" t="n">
-        <v>0.104</v>
+        <v>0.022</v>
       </c>
       <c r="F30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.041</v>
+        <v>0.023</v>
       </c>
       <c r="D31" t="n">
-        <v>-0</v>
+        <v>0.004</v>
       </c>
       <c r="E31" t="n">
-        <v>0.041</v>
+        <v>0.019</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.066</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0.059</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1308,7 +1308,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1317,18 +1317,45 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.022</v>
+        <v>-0.113</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.004</v>
+        <v>0.003</v>
       </c>
       <c r="E33" t="n">
-        <v>0.018</v>
+        <v>0.11</v>
       </c>
       <c r="F33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>baseline_manager_efficacy</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>-0.082</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="F34" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1388,13 +1415,13 @@
         <v>7220</v>
       </c>
       <c r="B2" t="n">
-        <v>554.8319074166568</v>
+        <v>554.825677797897</v>
       </c>
       <c r="C2" t="n">
-        <v>0.07201588164977409</v>
+        <v>0.07201547472434851</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2496221955703657</v>
+        <v>0.2496223031115245</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -1464,19 +1491,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.236944464107626</v>
+        <v>2.23749662500239</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3384250196146679</v>
+        <v>0.3387223052094513</v>
       </c>
       <c r="D2" t="n">
-        <v>1.573643614195615</v>
+        <v>1.573613106031481</v>
       </c>
       <c r="E2" t="n">
-        <v>2.900245314019636</v>
+        <v>2.901380143973298</v>
       </c>
       <c r="F2" t="n">
-        <v>3.846647276159917e-11</v>
+        <v>3.956536729345319e-11</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1516,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.181150802664234</v>
+        <v>0.1812064174144252</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06590363351848998</v>
+        <v>0.06590478100124786</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05198205451766694</v>
+        <v>0.0520354202429798</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3103195508108011</v>
+        <v>0.3103774145858706</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005982800716697941</v>
+        <v>0.005968288593448914</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,19 +1541,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2889210511748292</v>
+        <v>0.2889599816537746</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1525985701599981</v>
+        <v>0.1525998690311317</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.01016665043107556</v>
+        <v>-0.01013026569277259</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5880087527807341</v>
+        <v>0.5880502290003218</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05831260422500213</v>
+        <v>0.05828084846145002</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1566,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.005957694933862395</v>
+        <v>-0.005930239991922437</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1146433802895684</v>
+        <v>0.1146465029553819</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2306545913673455</v>
+        <v>-0.2306332567379359</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2187392014996207</v>
+        <v>0.218772776754091</v>
       </c>
       <c r="F5" t="n">
-        <v>0.958554832434062</v>
+        <v>0.9587467768438096</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1591,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2614273190347505</v>
+        <v>0.2614738833848432</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1392840286028366</v>
+        <v>0.1392815268346735</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.01156436064845606</v>
+        <v>-0.011512892922866</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5344189987179571</v>
+        <v>0.5344606596925525</v>
       </c>
       <c r="F6" t="n">
-        <v>0.06052675630474114</v>
+        <v>0.06047632629975165</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1616,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.01841397076183392</v>
+        <v>-0.01843610688784001</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1223193367586622</v>
+        <v>0.1223209403783178</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2581554654216383</v>
+        <v>-0.2581807445844141</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2213275238979704</v>
+        <v>0.2213085308087341</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8803384800164809</v>
+        <v>0.8801972744990099</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1641,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1905247839024713</v>
+        <v>0.1905828344073592</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1312065100950985</v>
+        <v>0.1312049657825513</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.06663525042111285</v>
+        <v>-0.06657417311925137</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4476848182260554</v>
+        <v>0.4477398419339698</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1464742032871121</v>
+        <v>0.1463464896656156</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,19 +1666,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.164771970074634</v>
+        <v>0.164757420387602</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1133318732696424</v>
+        <v>0.1133328992258047</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.05735441983432277</v>
+        <v>-0.05737098035848257</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3868983599835908</v>
+        <v>0.3868858211336866</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1459770678884148</v>
+        <v>0.146016320112753</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1691,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.2220479403681949</v>
+        <v>-0.2220465411067011</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1738904480020738</v>
+        <v>0.1738931113343997</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5628669557077947</v>
+        <v>-0.5628707764817383</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1187710749714047</v>
+        <v>0.1187776942683361</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2016228791937935</v>
+        <v>0.2016326256576764</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1716,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03288756718509719</v>
+        <v>0.03290455676826715</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1776097727247112</v>
+        <v>0.1776067110021227</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3152211906576813</v>
+        <v>-0.315198200208507</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3809963250278756</v>
+        <v>0.3810073137450413</v>
       </c>
       <c r="F11" t="n">
-        <v>0.853097617132373</v>
+        <v>0.8530200871491429</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1741,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.01926300923725721</v>
+        <v>-0.01924680994036938</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1857937530359848</v>
+        <v>0.1857900995638568</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3834120737403168</v>
+        <v>-0.3833887137696395</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3448860552658023</v>
+        <v>0.3448950938889008</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9174236707386756</v>
+        <v>0.9174912487776152</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1766,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02751012339829574</v>
+        <v>0.02754524401646694</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1635058900678632</v>
+        <v>0.1635056907376266</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.2929555323948815</v>
+        <v>-0.2929200210966256</v>
       </c>
       <c r="E13" t="n">
-        <v>0.347975779191473</v>
+        <v>0.3480105091295595</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8663853688450227</v>
+        <v>0.8662162356431101</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1791,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.2140509916498262</v>
+        <v>-0.2141644827938371</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1996415110470127</v>
+        <v>0.1996402222585082</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.6053411631211266</v>
+        <v>-0.6054521282860847</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1772391798214741</v>
+        <v>0.1771231626984105</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2836406395758079</v>
+        <v>0.2833823235331733</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1816,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1171045186779469</v>
+        <v>0.1171233896182655</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1619967599285948</v>
+        <v>0.1619877452742362</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2004032963942804</v>
+        <v>-0.2003667570560858</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4346123337501741</v>
+        <v>0.4346135362926168</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4697524708434644</v>
+        <v>0.4696561809599472</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1841,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.0127286824119694</v>
+        <v>-0.01274082353505155</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1645558921490834</v>
+        <v>0.1645459794204058</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3352523044680304</v>
+        <v>-0.3352450169999158</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3097949396440916</v>
+        <v>0.3097633699298127</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9383437421023142</v>
+        <v>0.9382813388160075</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1866,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.04675708148500214</v>
+        <v>-0.04674521195771184</v>
       </c>
       <c r="C17" t="n">
-        <v>0.176031274568947</v>
+        <v>0.1760224638325073</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3917720397928198</v>
+        <v>-0.3917429015394304</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2982578768228155</v>
+        <v>0.2982524776240068</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7905333934586962</v>
+        <v>0.7905750912287317</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1891,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.02301946934380628</v>
+        <v>-0.02287445724546811</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1644652153812268</v>
+        <v>0.1644573367348369</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3453653682006337</v>
+        <v>-0.3452049142391245</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2993264295130212</v>
+        <v>0.2994559997481883</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8886871854160944</v>
+        <v>0.8893786156956413</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1916,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.2146921070890922</v>
+        <v>-0.2147072225477657</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1515530665957196</v>
+        <v>0.1515491417724085</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.511730659363303</v>
+        <v>-0.5117380823096411</v>
       </c>
       <c r="E19" t="n">
-        <v>0.08234644518511855</v>
+        <v>0.08232363721410968</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1565959844710106</v>
+        <v>0.1565560792992995</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1941,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.005402522655627897</v>
+        <v>-0.005496453050048544</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1655922621823109</v>
+        <v>0.1655919716507671</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3299573926514712</v>
+        <v>-0.3300507536145296</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3191523473402154</v>
+        <v>0.3190578475144326</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9739732716462246</v>
+        <v>0.9735208789596658</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1966,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.2427296873564388</v>
+        <v>-0.2428197437973162</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1660896874446664</v>
+        <v>0.1660915324295564</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5682594929514992</v>
+        <v>-0.5683531654963131</v>
       </c>
       <c r="E21" t="n">
-        <v>0.08280011823862174</v>
+        <v>0.08271367790168074</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1438954327129228</v>
+        <v>0.1437512358288602</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1991,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.03768411407691186</v>
+        <v>-0.03762647872963693</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1797730666913064</v>
+        <v>0.1797711451000331</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3900328501821896</v>
+        <v>-0.389971448585226</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3146646220283659</v>
+        <v>0.3147184911259522</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8339639046817264</v>
+        <v>0.8342124101726425</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +2016,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.02464806102588241</v>
+        <v>-0.02464984097832305</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1900831223009976</v>
+        <v>0.1900772109899224</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3972041348047601</v>
+        <v>-0.3971943288003919</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3479080127529953</v>
+        <v>0.3478946468437458</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8968275912688044</v>
+        <v>0.8968169914779658</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2041,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2059416113771989</v>
+        <v>0.2059913401970664</v>
       </c>
       <c r="C24" t="n">
-        <v>0.09524738374795884</v>
+        <v>0.09524617696162553</v>
       </c>
       <c r="D24" t="n">
-        <v>0.01926016960953392</v>
+        <v>0.01931226368715172</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3926230531448639</v>
+        <v>0.3926704167069811</v>
       </c>
       <c r="F24" t="n">
-        <v>0.03060460934207493</v>
+        <v>0.03056229495900963</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2066,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.04452008568401997</v>
+        <v>0.04450087827793899</v>
       </c>
       <c r="C25" t="n">
-        <v>0.07833813972634333</v>
+        <v>0.07834143652701159</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1090198467954794</v>
+        <v>-0.1090455158121344</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1980600181635193</v>
+        <v>0.1980472723680124</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5698267649268596</v>
+        <v>0.5700094656902925</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2091,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.04831767222516932</v>
+        <v>0.04828306134397901</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1075095082429104</v>
+        <v>0.1075107282210875</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.1623970919265472</v>
+        <v>-0.1624340939210264</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2590324363768859</v>
+        <v>0.2590002166089845</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6531236814450445</v>
+        <v>0.6533595654050095</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2116,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.01812015855057378</v>
+        <v>0.01808879885203665</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1120508625951185</v>
+        <v>0.1120502614513933</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2014954965725048</v>
+        <v>-0.2015256780509909</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2377358136736524</v>
+        <v>0.2377032757550642</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8715313227345117</v>
+        <v>0.8717510489087302</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2141,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.04940558150093539</v>
+        <v>-0.04947691685693353</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1079780618094178</v>
+        <v>0.1079782814630219</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.2610386937678342</v>
+        <v>-0.2611104596369855</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1622275307659634</v>
+        <v>0.1621566259231184</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6472743129266691</v>
+        <v>0.6468003220383834</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2166,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0428013710423109</v>
+        <v>0.04279578165024722</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1082244098992596</v>
+        <v>0.1082268052729155</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.1693145746083381</v>
+        <v>-0.1693248588464967</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2549173166929599</v>
+        <v>0.2549164221469912</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6924833512519117</v>
+        <v>0.6925279175992387</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,19 +2191,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.4119231277135925</v>
+        <v>0.4113196490102574</v>
       </c>
       <c r="C30" t="n">
-        <v>0.03551662021466816</v>
+        <v>0.03542261130074707</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3423118312402556</v>
+        <v>0.3418926066224316</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4815344241869293</v>
+        <v>0.4807466913980831</v>
       </c>
       <c r="F30" t="n">
-        <v>4.216315028059068e-31</v>
+        <v>3.590526857595078e-31</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2212,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.440174177203154</v>
+        <v>-0.0102567328238261</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1799506899318473</v>
+        <v>0.005466971384185145</v>
       </c>
       <c r="D31" t="n">
-        <v>1.087477305943599</v>
+        <v>-0.02097179984134007</v>
       </c>
       <c r="E31" t="n">
-        <v>1.792871048462709</v>
+        <v>0.000458334193687869</v>
       </c>
       <c r="F31" t="n">
-        <v>1.212661290946233e-15</v>
+        <v>0.06063783793055883</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2210,23 +2237,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.01025948591986663</v>
+        <v>-0.02794199150770857</v>
       </c>
       <c r="C32" t="n">
-        <v>0.005466797757691274</v>
+        <v>0.01461303548762868</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.02097421263570586</v>
+        <v>-0.05658301476826649</v>
       </c>
       <c r="E32" t="n">
-        <v>0.000455240795972589</v>
+        <v>0.000699031752849355</v>
       </c>
       <c r="F32" t="n">
-        <v>0.06056056299802699</v>
+        <v>0.0558598029351637</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2235,23 +2262,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>baseline_manager_efficacy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.005696864427362678</v>
+        <v>0.457499591755983</v>
       </c>
       <c r="C33" t="n">
-        <v>0.00501867373111394</v>
+        <v>0.04667594573487312</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.01553328419050326</v>
+        <v>0.3660164191712857</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0041395553357779</v>
+        <v>0.5489827643406803</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2563194081069063</v>
+        <v>1.108011036419449e-22</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2260,23 +2287,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.02794494020865268</v>
+        <v>0.007974997448012033</v>
       </c>
       <c r="C34" t="n">
-        <v>0.01461262990600826</v>
+        <v>0.004378423414313862</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.05658516854384178</v>
+        <v>-0.0006065547531100314</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0006952881265364259</v>
+        <v>0.0165565496491341</v>
       </c>
       <c r="F34" t="n">
-        <v>0.05582712904150519</v>
+        <v>0.06854132100413772</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2312,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.007976972803062379</v>
+        <v>-0.00569513679584065</v>
       </c>
       <c r="C35" t="n">
-        <v>0.004378059075285194</v>
+        <v>0.00501887135034792</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0006038653066853337</v>
+        <v>-0.01553194388556248</v>
       </c>
       <c r="E35" t="n">
-        <v>0.01655781091281009</v>
+        <v>0.004141670293881182</v>
       </c>
       <c r="F35" t="n">
-        <v>0.06844981601298375</v>
+        <v>0.2564823750541115</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2310,23 +2337,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>baseline_manager_efficacy</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.4575134647665858</v>
+        <v>1.440054719716598</v>
       </c>
       <c r="C36" t="n">
-        <v>0.04666760652833871</v>
+        <v>0.1800941769943752</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3660466367263556</v>
+        <v>1.087076618982241</v>
       </c>
       <c r="E36" t="n">
-        <v>0.548980292806816</v>
+        <v>1.793032820450955</v>
       </c>
       <c r="F36" t="n">
-        <v>1.085758088206443e-22</v>
+        <v>1.28400845072088e-15</v>
       </c>
       <c r="G36" t="n">
         <v>0.05</v>
@@ -2343,7 +2370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2375,13 +2402,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.680600179802939</v>
+        <v>-2.774614073588893</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4771933030981503</v>
+        <v>0.5213956350107296</v>
       </c>
       <c r="D2" t="n">
-        <v>1.938181768273511e-08</v>
+        <v>1.029072958036132e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2391,13 +2418,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02542074333516161</v>
+        <v>-0.02531896946916939</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1002143663033998</v>
+        <v>0.1001870355608945</v>
       </c>
       <c r="D3" t="n">
-        <v>0.79975540801217</v>
+        <v>0.8004868915759116</v>
       </c>
     </row>
     <row r="4">
@@ -2407,13 +2434,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2244463748843409</v>
+        <v>0.2256150601556658</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2335027157442915</v>
+        <v>0.2336513202417123</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3364439424069162</v>
+        <v>0.3342414930584403</v>
       </c>
     </row>
     <row r="5">
@@ -2423,13 +2450,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8155080917228588</v>
+        <v>0.8160827895347564</v>
       </c>
       <c r="C5" t="n">
-        <v>0.173402651392118</v>
+        <v>0.1734116198833066</v>
       </c>
       <c r="D5" t="n">
-        <v>2.563995828054386e-06</v>
+        <v>2.525694832362337e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2439,13 +2466,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03527526670387308</v>
+        <v>0.03622598517976101</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1916882946919544</v>
+        <v>0.1914953081760687</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8539945454713548</v>
+        <v>0.8499562329133765</v>
       </c>
     </row>
     <row r="7">
@@ -2455,13 +2482,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2773648159307716</v>
+        <v>0.2771938342360029</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1901447102133385</v>
+        <v>0.1901314810930083</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1446466431125523</v>
+        <v>0.1448664442117522</v>
       </c>
     </row>
     <row r="8">
@@ -2471,13 +2498,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1036811851537241</v>
+        <v>0.1053581304950989</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1952515666982444</v>
+        <v>0.1953442667159788</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5954095400432469</v>
+        <v>0.5896481989107895</v>
       </c>
     </row>
     <row r="9">
@@ -2487,13 +2514,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8738774480300985</v>
+        <v>0.8758696511293145</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1695280942409139</v>
+        <v>0.1693371735726043</v>
       </c>
       <c r="D9" t="n">
-        <v>2.539495077342821e-07</v>
+        <v>2.311788629896114e-07</v>
       </c>
     </row>
     <row r="10">
@@ -2503,13 +2530,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.0445652077261707</v>
+        <v>-0.04427462059794601</v>
       </c>
       <c r="C10" t="n">
-        <v>0.260402103171632</v>
+        <v>0.2604040478124682</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8641137091517843</v>
+        <v>0.8649922202201166</v>
       </c>
     </row>
     <row r="11">
@@ -2519,13 +2546,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.2737623724798146</v>
+        <v>-0.2742205061505729</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2787881385465067</v>
+        <v>0.2787689544694696</v>
       </c>
       <c r="D11" t="n">
-        <v>0.326113242387764</v>
+        <v>0.3252710045288607</v>
       </c>
     </row>
     <row r="12">
@@ -2535,13 +2562,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08100487957118148</v>
+        <v>0.08193295015444199</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2596429772097172</v>
+        <v>0.2597818841250331</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7550514391424692</v>
+        <v>0.7524645599189482</v>
       </c>
     </row>
     <row r="13">
@@ -2551,13 +2578,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03917827337461754</v>
+        <v>0.03769699417328307</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2572958805743774</v>
+        <v>0.2573362415649831</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8789745077123743</v>
+        <v>0.8835351721093876</v>
       </c>
     </row>
     <row r="14">
@@ -2567,13 +2594,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.05296103812307935</v>
+        <v>-0.05102687086134956</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2610089865588724</v>
+        <v>0.2608488036216072</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8392062624375534</v>
+        <v>0.8449087216020077</v>
       </c>
     </row>
     <row r="15">
@@ -2583,13 +2610,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1181322726534161</v>
+        <v>0.1194505179052281</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2572294350577187</v>
+        <v>0.2572736242808293</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6460556128984086</v>
+        <v>0.6424373510261965</v>
       </c>
     </row>
     <row r="16">
@@ -2599,13 +2626,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.004000986240379481</v>
+        <v>-0.003394520999804357</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2383903410311192</v>
+        <v>0.2383941217340668</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9866094604655132</v>
+        <v>0.9886392149415411</v>
       </c>
     </row>
     <row r="17">
@@ -2615,13 +2642,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1057185310395306</v>
+        <v>0.1051737680003754</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2543340222421759</v>
+        <v>0.254498915914791</v>
       </c>
       <c r="D17" t="n">
-        <v>0.677652912256731</v>
+        <v>0.6794174396292662</v>
       </c>
     </row>
     <row r="18">
@@ -2631,13 +2658,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1377694895733254</v>
+        <v>-0.1377738518166134</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2636874203313636</v>
+        <v>0.2637734916431444</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6013412201546282</v>
+        <v>0.6014483864186216</v>
       </c>
     </row>
     <row r="19">
@@ -2647,13 +2674,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02557154094223237</v>
+        <v>-0.02393490642264756</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2527597901538116</v>
+        <v>0.2529805715426136</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9194160355966677</v>
+        <v>0.9246233049950211</v>
       </c>
     </row>
     <row r="20">
@@ -2663,13 +2690,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.07344622569376411</v>
+        <v>-0.07301273583929968</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2674578609541021</v>
+        <v>0.2675190900686553</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7836169672222787</v>
+        <v>0.7849106151948626</v>
       </c>
     </row>
     <row r="21">
@@ -2679,13 +2706,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2063167170305062</v>
+        <v>0.2069135147918242</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2442896532450728</v>
+        <v>0.2442870989291291</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3983578134719854</v>
+        <v>0.3969897777610698</v>
       </c>
     </row>
     <row r="22">
@@ -2695,13 +2722,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1704634573362028</v>
+        <v>-0.1717092932306339</v>
       </c>
       <c r="C22" t="n">
-        <v>0.269674845496591</v>
+        <v>0.2696190828094299</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5273167196806365</v>
+        <v>0.5242168027309898</v>
       </c>
     </row>
     <row r="23">
@@ -2711,13 +2738,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.5008110927334755</v>
+        <v>-0.5023322926397</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2870672180445716</v>
+        <v>0.2872431741192605</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0810583897517186</v>
+        <v>0.08032473613005431</v>
       </c>
     </row>
     <row r="24">
@@ -2727,13 +2754,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9366864721074268</v>
+        <v>0.9363452786511914</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1483430409733375</v>
+        <v>0.1483102369545482</v>
       </c>
       <c r="D24" t="n">
-        <v>2.713396260923871e-10</v>
+        <v>2.72929944135025e-10</v>
       </c>
     </row>
     <row r="25">
@@ -2743,13 +2770,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5776106069409677</v>
+        <v>-0.578051393721116</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1143619392421806</v>
+        <v>0.1144316984848932</v>
       </c>
       <c r="D25" t="n">
-        <v>4.401383208103854e-07</v>
+        <v>4.383605797803227e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2759,13 +2786,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2373161448441742</v>
+        <v>0.2362077053959269</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1503781926377481</v>
+        <v>0.1504768607120734</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1145360411757815</v>
+        <v>0.1164784602604647</v>
       </c>
     </row>
     <row r="27">
@@ -2775,13 +2802,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04350476117998643</v>
+        <v>-0.04595559996241676</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1611879340386415</v>
+        <v>0.1616567014228946</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7872365295400221</v>
+        <v>0.7761966040079398</v>
       </c>
     </row>
     <row r="28">
@@ -2791,13 +2818,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.07514354096975739</v>
+        <v>-0.07605967823822832</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1613683918223571</v>
+        <v>0.1614891401822257</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6414556246120158</v>
+        <v>0.6376482824383387</v>
       </c>
     </row>
     <row r="29">
@@ -2807,93 +2834,109 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09749293462742094</v>
+        <v>0.09626986426402341</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1543265796290169</v>
+        <v>0.1543844601757252</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5275624553510021</v>
+        <v>0.5329085436093777</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2280638724458788</v>
+        <v>-0.005017911290030882</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1146565719927948</v>
+        <v>0.00830544307228894</v>
       </c>
       <c r="D30" t="n">
-        <v>0.04668969945129902</v>
+        <v>0.5457296836910628</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.005012017390962181</v>
+        <v>-0.004305141260627514</v>
       </c>
       <c r="C31" t="n">
-        <v>0.008304876992454899</v>
+        <v>0.0222165512417676</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5461741835341518</v>
+        <v>0.8463475148043501</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>baseline_manager_efficacy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.002418133412192865</v>
+        <v>0.02937091471947225</v>
       </c>
       <c r="C32" t="n">
-        <v>0.007135781003458533</v>
+        <v>0.06892977188933355</v>
       </c>
       <c r="D32" t="n">
-        <v>0.7347043603418282</v>
+        <v>0.6700356258910083</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.004129656026475429</v>
+        <v>0.006290302487114363</v>
       </c>
       <c r="C33" t="n">
-        <v>0.02222260881033176</v>
+        <v>0.006868867616884186</v>
       </c>
       <c r="D33" t="n">
-        <v>0.8525770672961277</v>
+        <v>0.3597875728110738</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.006335499136474494</v>
+        <v>-0.002426755242405134</v>
       </c>
       <c r="C34" t="n">
-        <v>0.006871422968197173</v>
+        <v>0.007136997489227782</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3565249957666431</v>
+        <v>0.7338379468830419</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>is_new_manager</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.3248984989766635</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.2612255249732381</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.2135926414117477</v>
       </c>
     </row>
   </sheetData>
